--- a/forms/test-surveys/fd_test_health.xlsx
+++ b/forms/test-surveys/fd_test_health.xlsx
@@ -923,7 +923,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>regex(., 'HF-[0-9]{4}$')</t>
+          <t>regex(., '^HF-[0-9]{4}$')</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
